--- a/data/trans_camb/P19C03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 13,98</t>
+          <t>0,22; 13,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 1,87</t>
+          <t>-12,01; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,13; -4,09</t>
+          <t>-16,5; -4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 2,9</t>
+          <t>-13,26; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -3,79</t>
+          <t>-18,57; -4,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -9,51</t>
+          <t>-21,65; -8,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 7,8</t>
+          <t>-3,23; 7,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -2,42</t>
+          <t>-13,21; -3,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -8,26</t>
+          <t>-17,47; -8,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 53,06</t>
+          <t>0,51; 53,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 7,2</t>
+          <t>-35,99; 5,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,2; -14,36</t>
+          <t>-50,7; -16,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 10,12</t>
+          <t>-36,74; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -13,02</t>
+          <t>-50,87; -14,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; -33,24</t>
+          <t>-58,67; -30,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 27,76</t>
+          <t>-9,15; 26,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,95; -8,91</t>
+          <t>-38,81; -10,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -29,52</t>
+          <t>-51,49; -29,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 2,81</t>
+          <t>-12,71; 2,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -0,13</t>
+          <t>-14,69; 0,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,49; -11,02</t>
+          <t>-24,47; -11,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 1,64</t>
+          <t>-14,07; 1,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -0,59</t>
+          <t>-15,96; -1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,48; -14,47</t>
+          <t>-26,54; -14,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -1,03</t>
+          <t>-11,76; -1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -2,91</t>
+          <t>-12,92; -2,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,99; -15,26</t>
+          <t>-23,72; -14,54</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 9,38</t>
+          <t>-33,74; 7,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 0,46</t>
+          <t>-39,83; 1,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -37,76</t>
+          <t>-65,1; -38,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 5,17</t>
+          <t>-35,15; 3,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -2,34</t>
+          <t>-39,07; -3,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,36; -43,82</t>
+          <t>-64,79; -43,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,78; -3,23</t>
+          <t>-31,07; -3,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -8,66</t>
+          <t>-34,21; -7,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,64; -46,13</t>
+          <t>-62,38; -44,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 0,1</t>
+          <t>-12,48; -0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 0,59</t>
+          <t>-12,34; 1,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,63; -11,95</t>
+          <t>-35,25; -12,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 8,29</t>
+          <t>-11,35; 7,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 4,84</t>
+          <t>-15,98; 5,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; -6,86</t>
+          <t>-25,23; -6,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 0,41</t>
+          <t>-10,08; 0,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; -0,51</t>
+          <t>-11,05; -0,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-30,77; -12,65</t>
+          <t>-30,21; -12,86</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 0,36</t>
+          <t>-32,38; -0,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 1,77</t>
+          <t>-32,46; 3,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,76; -34,58</t>
+          <t>-86,69; -34,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 35,12</t>
+          <t>-29,72; 26,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 18,05</t>
+          <t>-44,66; 17,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,04; -22,55</t>
+          <t>-65,61; -23,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 1,34</t>
+          <t>-27,49; 1,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -1,61</t>
+          <t>-30,39; -1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,11; -37,41</t>
+          <t>-83,58; -37,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,81</t>
+          <t>-6,55; 2,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,63</t>
+          <t>-6,31; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -5,15</t>
+          <t>-13,81; -5,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 2,57</t>
+          <t>-8,38; 2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 2,75</t>
+          <t>-8,13; 2,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -12,71</t>
+          <t>-27,89; -12,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,78</t>
+          <t>-5,85; 0,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 1,33</t>
+          <t>-5,73; 1,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -10,2</t>
+          <t>-19,99; -10,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 6,38</t>
+          <t>-19,75; 7,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 9,25</t>
+          <t>-18,76; 8,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,77; -17,57</t>
+          <t>-41,66; -17,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 7,76</t>
+          <t>-21,81; 7,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 9,14</t>
+          <t>-20,85; 7,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,56; -36,62</t>
+          <t>-75,18; -36,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 2,59</t>
+          <t>-16,8; 2,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 4,24</t>
+          <t>-16,31; 4,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,21; -31,8</t>
+          <t>-58,7; -32,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 2,0</t>
+          <t>-12,63; 2,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 0,52</t>
+          <t>-14,03; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,09; -8,02</t>
+          <t>-22,52; -7,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,0; -0,37</t>
+          <t>-11,69; -0,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 0,39</t>
+          <t>-11,81; -0,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -1,96</t>
+          <t>-19,82; -1,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -1,69</t>
+          <t>-10,53; -1,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -1,13</t>
+          <t>-10,45; -1,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -6,13</t>
+          <t>-19,21; -5,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 5,7</t>
+          <t>-33,11; 8,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 2,64</t>
+          <t>-37,1; 4,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,62; -26,64</t>
+          <t>-58,71; -27,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,0; -1,1</t>
+          <t>-32,13; -1,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 1,28</t>
+          <t>-31,48; -0,12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,27; -5,44</t>
+          <t>-55,45; -4,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -5,13</t>
+          <t>-28,75; -3,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -3,28</t>
+          <t>-28,45; -4,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,29; -17,37</t>
+          <t>-53,21; -15,05</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 10,81</t>
+          <t>-6,04; 11,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 3,87</t>
+          <t>-12,39; 3,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -2,48</t>
+          <t>-23,7; -2,22</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,43</t>
+          <t>-3,7; 4,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -2,83</t>
+          <t>-11,14; -2,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,99; -8,02</t>
+          <t>-15,89; -8,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,42</t>
+          <t>-2,89; 4,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -2,82</t>
+          <t>-9,89; -3,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,95; -8,01</t>
+          <t>-16,08; -7,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 41,92</t>
+          <t>-17,14; 44,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 14,66</t>
+          <t>-35,19; 14,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,64; -6,86</t>
+          <t>-72,18; -6,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 17,87</t>
+          <t>-13,43; 16,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,92; -11,39</t>
+          <t>-38,76; -10,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,14; -31,26</t>
+          <t>-56,52; -33,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 17,45</t>
+          <t>-9,7; 15,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -10,99</t>
+          <t>-33,61; -11,41</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,6; -30,6</t>
+          <t>-55,89; -29,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,62</t>
+          <t>-4,56; 0,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,96</t>
+          <t>-7,22; -1,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -11,31</t>
+          <t>-18,73; -11,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -0,42</t>
+          <t>-5,35; -0,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -3,25</t>
+          <t>-8,39; -3,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -11,7</t>
+          <t>-18,14; -11,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,14; -0,77</t>
+          <t>-4,41; -0,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -3,45</t>
+          <t>-7,06; -3,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -12,37</t>
+          <t>-16,97; -12,16</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 2,0</t>
+          <t>-13,67; 1,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,41; -6,37</t>
+          <t>-21,56; -5,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,9; -36,61</t>
+          <t>-57,19; -36,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -1,66</t>
+          <t>-16,03; -1,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -10,74</t>
+          <t>-24,79; -11,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,37; -37,9</t>
+          <t>-55,41; -37,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,53; -2,46</t>
+          <t>-13,27; -2,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,25; -11,21</t>
+          <t>-21,59; -10,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-53,15; -39,83</t>
+          <t>-52,6; -38,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,58</t>
+          <t>-11,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-15,27</t>
+          <t>-15,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,57</t>
+          <t>-13,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 13,65</t>
+          <t>0,59; 14,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 1,34</t>
+          <t>-11,51; 1,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -4,28</t>
+          <t>-17,38; -5,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 1,72</t>
+          <t>-13,37; 2,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -4,49</t>
+          <t>-18,88; -4,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -8,43</t>
+          <t>-21,88; -8,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,09</t>
+          <t>-2,91; 7,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,22</t>
+          <t>-12,63; -2,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,47; -8,26</t>
+          <t>-17,21; -8,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-36,45%</t>
+          <t>-40,24%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-46,85%</t>
+          <t>-46,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-41,23%</t>
+          <t>-42,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 53,16</t>
+          <t>1,74; 53,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 5,34</t>
+          <t>-36,12; 6,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -16,09</t>
+          <t>-53,66; -20,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 5,79</t>
+          <t>-36,71; 7,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,87; -14,68</t>
+          <t>-52,25; -13,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -30,99</t>
+          <t>-58,39; -30,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 26,56</t>
+          <t>-9,34; 23,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,81; -10,95</t>
+          <t>-38,31; -7,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -29,26</t>
+          <t>-52,18; -31,41</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-17,86</t>
+          <t>-17,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,62</t>
+          <t>-19,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-19,38</t>
+          <t>-18,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 2,2</t>
+          <t>-12,55; 1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 0,42</t>
+          <t>-15,52; -0,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,47; -11,59</t>
+          <t>-24,08; -10,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 1,11</t>
+          <t>-14,41; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,96; -1,25</t>
+          <t>-16,17; -1,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -14,56</t>
+          <t>-25,9; -13,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -1,29</t>
+          <t>-11,39; -0,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -2,32</t>
+          <t>-13,7; -2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -14,54</t>
+          <t>-23,32; -14,58</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-53,64%</t>
+          <t>-53,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-55,61%</t>
+          <t>-52,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-54,93%</t>
+          <t>-53,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 7,91</t>
+          <t>-33,45; 5,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 1,47</t>
+          <t>-40,8; 0,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,1; -38,38</t>
+          <t>-65,29; -36,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 3,13</t>
+          <t>-35,23; 4,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -3,64</t>
+          <t>-39,72; -3,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,79; -43,78</t>
+          <t>-62,57; -41,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -3,85</t>
+          <t>-29,56; -1,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,21; -7,37</t>
+          <t>-35,74; -7,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -44,58</t>
+          <t>-61,39; -45,11</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-21,75</t>
+          <t>-12,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-15,56</t>
+          <t>-14,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-20,36</t>
+          <t>-13,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; -0,02</t>
+          <t>-12,38; 0,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 1,18</t>
+          <t>-11,74; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,25; -12,07</t>
+          <t>-18,39; -6,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 7,16</t>
+          <t>-11,98; 7,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 5,03</t>
+          <t>-16,75; 4,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,23; -6,61</t>
+          <t>-24,28; -5,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 0,49</t>
+          <t>-10,12; -0,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -0,54</t>
+          <t>-11,56; -0,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-30,21; -12,86</t>
+          <t>-18,54; -7,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-61,73%</t>
+          <t>-34,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-48,81%</t>
+          <t>-45,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-59,17%</t>
+          <t>-37,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,38; -0,19</t>
+          <t>-31,93; 1,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 3,71</t>
+          <t>-30,89; 3,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,69; -34,22</t>
+          <t>-48,28; -18,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 26,65</t>
+          <t>-31,57; 28,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 17,75</t>
+          <t>-44,42; 18,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,61; -23,49</t>
+          <t>-63,65; -17,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 1,31</t>
+          <t>-27,59; -0,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -1,6</t>
+          <t>-31,84; -1,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-83,58; -37,91</t>
+          <t>-49,51; -24,24</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,5</t>
+          <t>-10,85</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-18,92</t>
+          <t>-14,27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,73</t>
+          <t>-12,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 2,17</t>
+          <t>-6,38; 2,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 2,52</t>
+          <t>-6,5; 2,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -5,1</t>
+          <t>-15,57; -7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 2,51</t>
+          <t>-8,8; 1,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,61</t>
+          <t>-8,32; 2,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -12,44</t>
+          <t>-19,24; -10,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,75</t>
+          <t>-6,09; 0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 1,32</t>
+          <t>-5,35; 1,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,99; -10,36</t>
+          <t>-15,2; -8,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,42%</t>
+          <t>-34,76%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,82%</t>
+          <t>-39,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,49%</t>
+          <t>-36,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 7,61</t>
+          <t>-19,49; 7,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 8,43</t>
+          <t>-19,53; 9,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,66; -17,91</t>
+          <t>-44,93; -23,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 7,52</t>
+          <t>-22,43; 5,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 7,8</t>
+          <t>-21,54; 6,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,18; -36,42</t>
+          <t>-48,96; -30,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 2,52</t>
+          <t>-17,55; 2,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 4,25</t>
+          <t>-15,31; 3,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,7; -32,08</t>
+          <t>-43,48; -29,07</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-15,27</t>
+          <t>-13,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-13,47</t>
+          <t>-14,97</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,1</t>
+          <t>-14,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 2,23</t>
+          <t>-12,28; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 1,21</t>
+          <t>-13,03; 1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -7,93</t>
+          <t>-21,4; -6,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -0,36</t>
+          <t>-12,39; -0,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -0,06</t>
+          <t>-11,67; 0,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -1,97</t>
+          <t>-20,17; -9,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,53; -1,17</t>
+          <t>-10,97; -1,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -1,48</t>
+          <t>-10,5; -1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,21; -5,31</t>
+          <t>-18,84; -10,15</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-45,64%</t>
+          <t>-41,21%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-39,56%</t>
+          <t>-43,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,67%</t>
+          <t>-42,93%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 8,32</t>
+          <t>-32,4; 7,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 4,44</t>
+          <t>-34,64; 3,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,71; -27,39</t>
+          <t>-55,21; -22,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,13; -1,15</t>
+          <t>-32,64; -2,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,48; -0,12</t>
+          <t>-30,94; 2,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -4,65</t>
+          <t>-53,02; -32,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,75; -3,77</t>
+          <t>-29,3; -4,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,45; -4,35</t>
+          <t>-28,9; -4,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,21; -15,05</t>
+          <t>-50,5; -33,05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-14,22</t>
+          <t>-14,86</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-11,96</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 11,25</t>
+          <t>-6,17; 11,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 3,69</t>
+          <t>-12,56; 4,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,7; -2,22</t>
+          <t>-23,9; -3,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,05</t>
+          <t>-3,72; 4,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -2,56</t>
+          <t>-10,96; -3,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -8,3</t>
+          <t>-15,4; -7,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,06</t>
+          <t>-3,11; 4,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -3,09</t>
+          <t>-10,07; -2,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -7,94</t>
+          <t>-16,37; -8,76</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-46,91%</t>
+          <t>-49,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-45,3%</t>
+          <t>-44,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 44,07</t>
+          <t>-18,12; 44,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 14,81</t>
+          <t>-36,1; 20,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,18; -6,5</t>
+          <t>-72,44; -12,17</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 16,14</t>
+          <t>-13,18; 16,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,76; -10,15</t>
+          <t>-38,66; -12,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-56,52; -33,58</t>
+          <t>-53,6; -30,61</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 15,84</t>
+          <t>-10,45; 16,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,61; -11,41</t>
+          <t>-34,67; -9,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-55,89; -29,89</t>
+          <t>-56,28; -33,73</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-14,15</t>
+          <t>-12,89</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-14,81</t>
+          <t>-13,87</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-14,49</t>
+          <t>-13,39</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,44</t>
+          <t>-4,66; 0,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -1,67</t>
+          <t>-7,04; -1,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,73; -11,42</t>
+          <t>-15,38; -10,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,57</t>
+          <t>-5,43; -0,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -3,61</t>
+          <t>-8,37; -3,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-18,14; -11,67</t>
+          <t>-16,28; -11,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; -0,7</t>
+          <t>-4,34; -0,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -3,41</t>
+          <t>-7,04; -3,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -12,16</t>
+          <t>-15,02; -11,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-44,25%</t>
+          <t>-40,3%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-46,17%</t>
+          <t>-43,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-45,24%</t>
+          <t>-41,82%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 1,47</t>
+          <t>-14,02; 1,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,56; -5,44</t>
+          <t>-21,07; -6,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,19; -36,63</t>
+          <t>-46,0; -34,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -1,71</t>
+          <t>-16,4; -1,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-24,79; -11,28</t>
+          <t>-25,04; -11,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,41; -37,32</t>
+          <t>-48,28; -38,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,27; -2,17</t>
+          <t>-13,17; -2,36</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -10,95</t>
+          <t>-21,23; -11,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-52,6; -38,94</t>
+          <t>-45,62; -38,15</t>
         </is>
       </c>
     </row>
